--- a/data/trans_camb/IP2004-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 7,63</t>
+          <t>-4,27; 7,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 12,24</t>
+          <t>-0,94; 12,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 0,0</t>
+          <t>-9,23; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 21,13</t>
+          <t>5,15; 19,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,43</t>
+          <t>1,78; 12,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 12,25</t>
+          <t>2,64; 11,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,53</t>
+          <t>1,49; 9,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 0,48</t>
+          <t>-3,89; 0,42</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-65,05; —</t>
+          <t>-64,11; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,38; —</t>
+          <t>34,96; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; —</t>
+          <t>-9,53; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,97; -4,14</t>
+          <t>-16,4; -4,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -6,69</t>
+          <t>-17,71; -6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,64; -7,25</t>
+          <t>-18,05; -7,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,48; -5,77</t>
+          <t>-18,33; -5,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,53; -6,07</t>
+          <t>-18,41; -5,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,37; -8,2</t>
+          <t>-18,82; -8,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,32; -6,84</t>
+          <t>-14,7; -6,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -7,67</t>
+          <t>-15,61; -7,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -9,02</t>
+          <t>-16,19; -8,71</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-95,1; -35,99</t>
+          <t>-95,54; -35,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -60,42</t>
+          <t>-100,0; -64,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -81,85</t>
+          <t>-100,0; -75,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -37,23</t>
+          <t>-100,0; -45,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-95,9; -49,14</t>
+          <t>-96,27; -54,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -78,54</t>
+          <t>-100,0; -83,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-94,63; -54,3</t>
+          <t>-93,85; -58,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-97,24; -70,34</t>
+          <t>-97,46; -70,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-99,04; -89,29</t>
+          <t>-99,04; -88,45</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 8,73</t>
+          <t>-1,05; 9,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 10,06</t>
+          <t>-0,74; 9,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,05</t>
+          <t>-3,2; 2,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,14</t>
+          <t>-1,58; 3,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,36</t>
+          <t>-1,58; 3,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 11,96</t>
+          <t>0,21; 12,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,81</t>
+          <t>-0,6; 4,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 4,74</t>
+          <t>-0,54; 5,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 6,37</t>
+          <t>-0,11; 7,14</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-70,32; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 6,32</t>
+          <t>-2,53; 6,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 16,91</t>
+          <t>2,68; 16,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 6,13</t>
+          <t>-3,55; 6,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,33</t>
+          <t>1,75; 10,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 9,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,79</t>
+          <t>-0,93; 4,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 10,66</t>
+          <t>3,05; 10,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,06</t>
+          <t>-0,72; 5,21</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,91; —</t>
+          <t>6,28; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,26; —</t>
+          <t>55,08; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 16,04</t>
+          <t>-3,7; 15,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,9; -1,6</t>
+          <t>-13,88; -1,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 1,7</t>
+          <t>-12,05; 1,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 15,18</t>
+          <t>0,14; 14,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,92</t>
+          <t>-4,82; 2,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 3,7</t>
+          <t>-4,73; 2,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 12,84</t>
+          <t>0,35; 12,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -0,04</t>
+          <t>-7,48; -0,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 1,52</t>
+          <t>-6,01; 1,52</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,69; —</t>
+          <t>-65,59; 853,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 1057,68</t>
+          <t>-17,78; 1111,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,14 +1687,14 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 0,0</t>
+          <t>-6,83; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,73</t>
+          <t>-2,77; 6,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,0</t>
+          <t>-6,86; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 0,0</t>
+          <t>-6,52; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,33</t>
+          <t>-4,34; 3,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,0</t>
+          <t>-6,67; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; -0,51</t>
+          <t>-5,09; -0,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,75</t>
+          <t>-2,39; 3,58</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,47; -0,52</t>
+          <t>-5,2; -0,52</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,11</t>
+          <t>1,57; 7,37</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,33</t>
+          <t>0,47; 4,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,17</t>
+          <t>1,3; 7,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,91</t>
+          <t>-2,21; 2,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,05</t>
+          <t>-3,29; 1,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,15; 8,82</t>
+          <t>1,0; 8,75</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,87</t>
+          <t>0,23; 3,78</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,75</t>
+          <t>-0,83; 1,8</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,87</t>
+          <t>1,83; 6,83</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,23; —</t>
+          <t>-17,43; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-61,57; —</t>
+          <t>-54,37; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>44,0; —</t>
+          <t>63,97; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,22</t>
+          <t>-3,72; 1,52</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,47; -0,71</t>
+          <t>-5,4; -0,61</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,57; -1,04</t>
+          <t>-5,6; -0,96</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,76</t>
+          <t>-3,65; 0,87</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,84</t>
+          <t>-5,12; -1,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,99</t>
+          <t>-3,69; 1,4</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,38</t>
+          <t>-2,92; 0,58</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -1,2</t>
+          <t>-4,09; -1,09</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,36</t>
+          <t>-3,55; -0,29</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-91,45; 114,89</t>
+          <t>-87,37; 162,6</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 126,24</t>
+          <t>-100,0; 148,97</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 266,18</t>
+          <t>-100,0; 301,23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-81,66; 36,53</t>
+          <t>-79,46; 51,91</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -54,99</t>
+          <t>-100,0; -45,86</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,59</t>
+          <t>-100,0; 21,3</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,34</t>
+          <t>-1,89; 1,33</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,97</t>
+          <t>-2,12; 1,02</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,89; -1,07</t>
+          <t>-3,59; -0,87</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,8</t>
+          <t>-2,18; 0,84</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,88; -0,39</t>
+          <t>-2,85; -0,28</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,51</t>
+          <t>-2,38; 0,51</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,5</t>
+          <t>-1,66; 0,59</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,02</t>
+          <t>-2,1; -0,15</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,53; -0,55</t>
+          <t>-2,69; -0,56</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 50,94</t>
+          <t>-45,27; 48,72</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 36,35</t>
+          <t>-49,18; 42,93</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-84,58; -29,27</t>
+          <t>-83,86; -28,78</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-54,11; 35,67</t>
+          <t>-55,97; 34,86</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-71,9; -9,91</t>
+          <t>-72,04; -6,62</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 22,01</t>
+          <t>-60,09; 19,8</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 20,62</t>
+          <t>-43,17; 20,96</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 2,49</t>
+          <t>-54,02; -3,87</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-66,06; -17,16</t>
+          <t>-65,66; -19,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 7,44</t>
+          <t>-4,56; 7,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 12,9</t>
+          <t>-1,55; 12,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 0,0</t>
+          <t>-9,48; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 19,36</t>
+          <t>5,56; 20,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,09</t>
+          <t>1,03; 12,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,81</t>
+          <t>2,19; 12,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 9,23</t>
+          <t>1,12; 9,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,42</t>
+          <t>-4,11; 0,39</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,11; —</t>
+          <t>-69,5; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,96; —</t>
+          <t>7,47; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,53; —</t>
+          <t>-43,24; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,4; -4,66</t>
+          <t>-16,1; -4,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -6,91</t>
+          <t>-17,81; -7,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,05; -7,24</t>
+          <t>-18,26; -7,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,33; -5,98</t>
+          <t>-17,58; -5,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -5,93</t>
+          <t>-17,76; -5,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -8,04</t>
+          <t>-19,02; -8,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -6,86</t>
+          <t>-15,0; -6,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,61; -7,57</t>
+          <t>-15,88; -7,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,19; -8,71</t>
+          <t>-16,82; -8,92</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-95,54; -35,53</t>
+          <t>-100,0; -36,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -64,45</t>
+          <t>-100,0; -67,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -75,37</t>
+          <t>-100,0; -81,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -45,67</t>
+          <t>-100,0; -33,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-96,27; -54,21</t>
+          <t>-96,05; -50,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -83,17</t>
+          <t>-100,0; -81,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-93,85; -58,95</t>
+          <t>-95,12; -60,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-97,46; -70,0</t>
+          <t>-97,36; -69,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-99,04; -88,45</t>
+          <t>-98,99; -88,31</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,0</t>
+          <t>-1,05; 9,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 9,94</t>
+          <t>-0,77; 10,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,14</t>
+          <t>-3,2; 2,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,91</t>
+          <t>-1,58; 3,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 12,25</t>
+          <t>0,42; 11,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,53</t>
+          <t>-0,71; 4,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,04</t>
+          <t>-0,56; 5,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 7,14</t>
+          <t>-0,25; 6,49</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,32; —</t>
+          <t>-84,36; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 6,65</t>
+          <t>-2,29; 7,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 16,55</t>
+          <t>2,21; 15,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 6,15</t>
+          <t>-3,47; 6,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,23</t>
+          <t>1,76; 10,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,03</t>
+          <t>0,0; 10,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 4,18</t>
+          <t>-0,65; 3,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 10,82</t>
+          <t>2,96; 11,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,21</t>
+          <t>-0,96; 4,86</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,28; —</t>
+          <t>-22,58; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>55,08; —</t>
+          <t>45,83; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 15,71</t>
+          <t>-3,64; 16,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -1,6</t>
+          <t>-15,18; -1,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 1,68</t>
+          <t>-11,95; 1,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 14,79</t>
+          <t>0,16; 15,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 2,96</t>
+          <t>-4,71; 2,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 2,94</t>
+          <t>-5,26; 2,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 12,62</t>
+          <t>0,83; 12,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,48; -0,06</t>
+          <t>-6,75; 0,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 1,52</t>
+          <t>-5,95; 1,45</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,59; 853,46</t>
+          <t>-66,43; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 1111,16</t>
+          <t>-12,79; 1234,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1762,42 +1762,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,73</t>
+          <t>-2,77; 6,75</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 0,0</t>
+          <t>-6,8; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,0</t>
+          <t>-7,16; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 3,58</t>
+          <t>-4,23; 4,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 0,0</t>
+          <t>-7,73; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,52</t>
+          <t>-5,31; -0,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,58</t>
+          <t>-2,47; 3,6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -0,52</t>
+          <t>-5,27; -0,52</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,37</t>
+          <t>1,45; 7,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,27</t>
+          <t>0,46; 4,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,43</t>
+          <t>1,37; 7,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,74</t>
+          <t>-2,18; 2,71</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,03</t>
+          <t>-3,34; 1,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,75</t>
+          <t>1,07; 8,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,78</t>
+          <t>0,26; 3,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,8</t>
+          <t>-0,64; 1,94</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,83</t>
+          <t>2,02; 6,89</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,43; —</t>
+          <t>-41,34; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-54,37; —</t>
+          <t>-34,96; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>63,97; —</t>
+          <t>111,03; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,52</t>
+          <t>-4,24; 1,52</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,4; -0,61</t>
+          <t>-5,21; -0,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,6; -0,96</t>
+          <t>-6,06; -0,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,87</t>
+          <t>-3,72; 1,06</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -1,08</t>
+          <t>-4,92; -0,84</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,4</t>
+          <t>-3,69; 1,41</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,58</t>
+          <t>-2,93; 0,48</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -1,09</t>
+          <t>-4,06; -1,19</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; -0,29</t>
+          <t>-3,56; -0,4</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-87,37; 162,6</t>
+          <t>-90,87; 184,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 148,97</t>
+          <t>-100,0; 134,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 301,23</t>
+          <t>-100,0; 252,03</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-79,46; 51,91</t>
+          <t>-81,07; 45,53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -45,86</t>
+          <t>-100,0; -56,58</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,3</t>
+          <t>-100,0; 1,13</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,33</t>
+          <t>-1,83; 1,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,02</t>
+          <t>-2,33; 0,93</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -0,87</t>
+          <t>-3,58; -0,88</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,84</t>
+          <t>-2,24; 0,89</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,85; -0,28</t>
+          <t>-2,89; -0,22</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,51</t>
+          <t>-2,32; 0,59</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,59</t>
+          <t>-1,58; 0,64</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,15</t>
+          <t>-2,18; -0,06</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,69; -0,56</t>
+          <t>-2,57; -0,53</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-45,27; 48,72</t>
+          <t>-43,62; 62,47</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 42,93</t>
+          <t>-52,41; 35,3</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-83,86; -28,78</t>
+          <t>-83,07; -26,95</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 34,86</t>
+          <t>-57,38; 38,24</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-72,04; -6,62</t>
+          <t>-73,01; -4,54</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 19,8</t>
+          <t>-59,35; 26,08</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 20,96</t>
+          <t>-40,86; 23,97</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-54,02; -3,87</t>
+          <t>-54,36; -0,63</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-65,66; -19,61</t>
+          <t>-66,2; -18,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,95</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,78</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,72</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-2,72</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,95</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,43</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-0,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 7,75</t>
+          <t>5,33; 21,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 12,14</t>
+          <t>1,78; 12,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 0,0</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 20,09</t>
+          <t>-4,23; 7,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 12,88</t>
+          <t>-1,66; 12,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>-9,46; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 12,5</t>
+          <t>2,55; 12,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,22</t>
+          <t>1,12; 9,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,39</t>
+          <t>-3,49; 0,47</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>51,39%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>173,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>504,79%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-69,48%</t>
+          <t>-69,34%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,5; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,05; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,47; —</t>
+          <t>33,38; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,24; —</t>
+          <t>-7,38; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-11,58</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-11,4</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-12,91</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-10,06</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-11,74</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-12,08</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-11,58</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,4</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,8</t>
+          <t>-12,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-12,47</t>
+          <t>-12,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,1; -4,26</t>
+          <t>-18,48; -5,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,81; -7,19</t>
+          <t>-17,53; -6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,26; -7,23</t>
+          <t>-19,48; -8,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,58; -5,64</t>
+          <t>-15,97; -4,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,76; -5,91</t>
+          <t>-18,03; -6,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,02; -8,1</t>
+          <t>-18,56; -7,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,0; -6,56</t>
+          <t>-15,32; -6,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,88; -7,73</t>
+          <t>-15,78; -7,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,82; -8,92</t>
+          <t>-16,67; -9,09</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-86,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-84,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-96,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-81,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-94,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-97,33%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-86,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-84,92%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-95,35%</t>
+          <t>-97,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-96,32%</t>
+          <t>-96,57%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -36,86</t>
+          <t>-100,0; -37,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -67,69</t>
+          <t>-95,9; -49,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -81,24</t>
+          <t>-100,0; -81,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -33,02</t>
+          <t>-95,1; -35,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-96,05; -50,32</t>
+          <t>-100,0; -60,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -81,57</t>
+          <t>-100,0; -79,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-95,12; -60,85</t>
+          <t>-94,63; -54,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-97,36; -69,93</t>
+          <t>-97,24; -70,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-98,99; -88,31</t>
+          <t>-99,09; -90,07</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,24</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,04</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>1,66</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,46</t>
+          <t>-1,58; 3,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 10,03</t>
+          <t>-1,58; 4,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,1</t>
+          <t>0,24; 8,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,14</t>
+          <t>-1,04; 8,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,59</t>
+          <t>-0,74; 10,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 11,91</t>
+          <t>-2,14; 3,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,83</t>
+          <t>-0,83; 4,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,21</t>
+          <t>-0,75; 4,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 6,49</t>
+          <t>-0,44; 4,65</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38,13%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>410,86%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>256,09%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>287,33%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-1,98%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38,13%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>553,58%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>252,01%</t>
+          <t>180,76%</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>-100,0; —</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,36; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8,19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 7,03</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 15,5</t>
+          <t>1,75; 10,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 6,38</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>-2,43; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,05</t>
+          <t>2,18; 16,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,19</t>
+          <t>-3,27; 6,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,95</t>
+          <t>-0,85; 3,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 11,34</t>
+          <t>3,18; 10,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,86</t>
+          <t>-0,7; 5,53</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>90,7%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>413,43%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>35,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>157,32%</t>
+          <t>168,74%</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,58; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-43,91; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>45,83; —</t>
+          <t>42,26; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,57</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,32</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-5,21</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-3,55</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6,57</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-3,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-1,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 16,33</t>
+          <t>0,09; 15,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,18; -1,6</t>
+          <t>-4,79; 2,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 1,69</t>
+          <t>-4,72; 4,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 15,73</t>
+          <t>-3,66; 16,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 2,93</t>
+          <t>-13,9; -1,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 2,71</t>
+          <t>-11,41; 1,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 12,44</t>
+          <t>-0,01; 12,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 0,53</t>
+          <t>-6,99; -0,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,45</t>
+          <t>-5,89; 1,72</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>421,93%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-7,92%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-4,9%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>102,16%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-68,2%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>421,93%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-7,92%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-14,35%</t>
+          <t>-66,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-55,4%</t>
+          <t>-51,97%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,43; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,69; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 1234,15</t>
+          <t>-14,28; 1057,68</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,15</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,68</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-2,15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-1,37</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,31</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>-1,37</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 0,0</t>
+          <t>-7,85; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,75</t>
+          <t>-4,18; 4,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 0,0</t>
+          <t>-7,43; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 0,0</t>
+          <t>-6,87; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 4,4</t>
+          <t>-2,73; 6,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 0,0</t>
+          <t>-6,41; 0,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,31; -0,52</t>
+          <t>-4,52; -0,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 3,6</t>
+          <t>-2,36; 3,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -0,52</t>
+          <t>-4,47; -0,52</t>
         </is>
       </c>
     </row>
@@ -1815,22 +1815,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>-31,87%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>95,4%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-31,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,57</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4,92</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>3,41</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,54</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,29</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>4,34</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,34</t>
+          <t>-2,09; 2,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,34</t>
+          <t>-2,81; 1,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,68</t>
+          <t>1,47; 9,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,71</t>
+          <t>1,26; 7,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,03</t>
+          <t>0,46; 4,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,25</t>
+          <t>1,22; 7,87</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,79</t>
+          <t>0,13; 3,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,94</t>
+          <t>-0,89; 1,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,89</t>
+          <t>2,31; 7,44</t>
         </is>
       </c>
     </row>
@@ -2026,34 +2026,34 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-51,82%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>444,38%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-51,82%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>387,74%</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>314,78%</t>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>705,78%</t>
+          <t>774,82%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,93; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,34; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-34,96; —</t>
+          <t>-61,57; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>111,03; —</t>
+          <t>55,73; —</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-1,2</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-2,38</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>-1,34</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-1,1</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-2,39</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>-2,74</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-2,38</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>-1,16</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,95</t>
+          <t>-2,0</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,52</t>
+          <t>-4,0; 0,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,21; -0,44</t>
+          <t>-5,17; -0,84</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,95</t>
+          <t>-3,86; 0,82</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 1,06</t>
+          <t>-3,97; 1,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,92; -0,84</t>
+          <t>-5,47; -0,71</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,41</t>
+          <t>-5,57; -1,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,48</t>
+          <t>-3,09; 0,38</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,06; -1,19</t>
+          <t>-4,23; -1,2</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,4</t>
+          <t>-3,72; -0,49</t>
         </is>
       </c>
     </row>
@@ -2242,34 +2242,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-50,61%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-56,19%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-40,34%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-87,16%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-50,61%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-52,78%</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>-45,27%</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-76,09%</t>
+          <t>-78,32%</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-90,87; 184,5</t>
+          <t>-100,0; 126,24</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2305,37 +2305,37 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 302,54</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,49</t>
+          <t>-91,45; 114,89</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 29,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 252,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-81,07; 45,53</t>
+          <t>-81,66; 36,53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -56,58</t>
+          <t>-100,0; -54,99</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,13</t>
+          <t>-100,0; 28,16</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-0,9</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-0,26</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-0,61</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-2,26</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,49</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,52</t>
+          <t>-2,1; 0,8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,93</t>
+          <t>-2,88; -0,39</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,88</t>
+          <t>-2,27; 0,46</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,89</t>
+          <t>-1,85; 1,34</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,89; -0,22</t>
+          <t>-2,29; 0,97</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,59</t>
+          <t>-3,76; -0,88</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,64</t>
+          <t>-1,61; 0,5</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,18; -0,06</t>
+          <t>-2,06; -0,02</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,53</t>
+          <t>-2,47; -0,46</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-22,98%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-48,4%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-28,37%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-7,7%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-17,67%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-65,99%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-22,98%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-48,4%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-27,92%</t>
+          <t>-62,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-46,55%</t>
+          <t>-45,34%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 62,47</t>
+          <t>-54,11; 35,67</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 35,3</t>
+          <t>-71,9; -9,91</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-83,07; -26,95</t>
+          <t>-57,99; 19,65</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 38,24</t>
+          <t>-43,6; 50,94</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-73,01; -4,54</t>
+          <t>-51,94; 36,35</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-59,35; 26,08</t>
+          <t>-83,11; -18,52</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 23,97</t>
+          <t>-40,92; 20,62</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-54,36; -0,63</t>
+          <t>-54,62; 2,49</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-66,2; -18,78</t>
+          <t>-64,98; -14,68</t>
         </is>
       </c>
     </row>
